--- a/public/templates/請求書他会社.xlsx
+++ b/public/templates/請求書他会社.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bd8b67dbe05400/ドキュメント/ケアサービス　たんでん/各種資料　原本/請求書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26bd8b67dbe05400/ドキュメント/ケアサービス　たんでん/各種資料　原本/請求書/アプリ用テンプレ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{6226EBAE-E707-43D0-BB74-24A32D4CA836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B44F71-9827-4FD1-9977-91F9B86A7228}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{6226EBAE-E707-43D0-BB74-24A32D4CA836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E23ED0-839E-4AB7-93F1-F1C90B8760A0}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5209DA7A-5152-4F99-B3B1-55AC7DC7D125}"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <r>
       <t>請求書</t>
@@ -281,26 +281,6 @@
     <t>合計</t>
   </si>
   <si>
-    <t>有料老人ホーム　サンライフ東駅</t>
-    <rPh sb="0" eb="4">
-      <t>ユウリョウロウジン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒガシエキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>齋藤俊子</t>
-    <rPh sb="0" eb="2">
-      <t>サイトウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トシコ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>誠に有り難うございます。</t>
   </si>
   <si>
@@ -349,6 +329,13 @@
       <t>カ</t>
     </rPh>
     <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>有料老人ホーム　</t>
+    <rPh sb="0" eb="4">
+      <t>ユウリョウロウジン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -1218,10 +1205,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1570,7 +1553,7 @@
       <c r="G2" s="31"/>
       <c r="H2" s="32"/>
       <c r="I2" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J2" s="34"/>
       <c r="K2" s="34"/>
@@ -1582,7 +1565,7 @@
     </row>
     <row r="3" spans="1:20" ht="21.75" customHeight="1">
       <c r="A3" s="35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="36"/>
       <c r="C3" s="36"/>
@@ -1602,7 +1585,7 @@
     </row>
     <row r="4" spans="1:20" ht="14.25" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -1622,7 +1605,7 @@
     </row>
     <row r="5" spans="1:20" ht="41.25" customHeight="1">
       <c r="A5" s="39" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="40"/>
@@ -1631,18 +1614,16 @@
       <c r="F5" s="40"/>
       <c r="G5" s="40"/>
       <c r="H5" s="38"/>
-      <c r="I5" s="25" t="s">
-        <v>22</v>
-      </c>
+      <c r="I5" s="25"/>
       <c r="J5" s="41"/>
       <c r="K5" s="41"/>
       <c r="L5" s="41"/>
       <c r="M5" s="42" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N5" s="42">
         <f>I13</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>1</v>
@@ -1752,9 +1733,9 @@
       <c r="F11" s="61"/>
       <c r="G11" s="47"/>
       <c r="H11" s="47"/>
-      <c r="I11" s="89" t="str">
+      <c r="I11" s="89">
         <f>I5</f>
-        <v>齋藤俊子</v>
+        <v>0</v>
       </c>
       <c r="J11" s="62"/>
       <c r="K11" s="62"/>
@@ -1798,9 +1779,7 @@
       <c r="H13" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="3">
-        <v>6</v>
-      </c>
+      <c r="I13" s="3"/>
       <c r="J13" s="69" t="s">
         <v>8</v>
       </c>
@@ -2175,7 +2154,7 @@
       <c r="G31" s="91"/>
       <c r="H31" s="91"/>
       <c r="I31" s="113" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J31" s="114"/>
       <c r="K31" s="114"/>
@@ -2293,10 +2272,10 @@
       <c r="B37" s="103"/>
       <c r="C37" s="103"/>
       <c r="D37" s="93" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E37" s="93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F37" s="103"/>
       <c r="G37" s="104"/>
